--- a/healthcare_surveys/013_public_health_data_ethics_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/013_public_health_data_ethics_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>public_health_data_ethics_survey_form</t>
+          <t>Public Health Data Ethics Survey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>survey_participants</t>
+          <t>participant_information</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>what_do_you_do</t>
+          <t>What do you do in your daily work or activities?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>demographics</t>
+          <t>demographic_information</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>demographic_information</t>
+          <t>What are your demographic information (age, gender, occupation)?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>survey_attitudes</t>
+          <t>anonymous_data_concerns</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>attitude_towards_using_anonymous_health_data</t>
+          <t>How do you feel about using anonymous health data?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>survey_priorities</t>
+          <t>data_privacy_priority</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>importance_of_health_data_privacy</t>
+          <t>How important do you feel about health data privacy?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,19 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>data_use_concerns</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
+          <t>What concerns do you have about using anonymous health data?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -657,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>data_use_attitudes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>What do you think about the use of anonymous health data?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -680,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>survey_concerns</t>
+          <t>likelihood_of_use</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>concerns_about_using_anonymous_data</t>
+          <t>How likely are you to use anonymous health data?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -703,46 +699,46 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>participation_feelings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>How do you feel about your own participation in the survey?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>survey_satisfaction</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>How satisfied are you with the survey?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -754,62 +750,58 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>recommendation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
+          <t>Would you like to be informed about any changes in your health data?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>participant_info_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>Would you recommend this survey to others?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>participant_info_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>How would you like to be informed about any changes in your health data?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,448 +814,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>survey_particip</t>
+          <t>participant_info_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>participant_information</t>
+          <t>How would you like to be informed about the use of your health data?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Enter a number</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>survey_particip</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>participant_information</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Enter participant information</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1280,12 +845,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1308,697 +873,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>survey_attitudes_choices</t>
+          <t>anonymous_data_concerns_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>survey_attitudes_choices</t>
+          <t>anonymous_data_concerns_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>survey_attitudes_choices</t>
+          <t>data_privacy_priority_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'undecided'}</t>
+          <t>very_important</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Undecided'}</t>
+          <t>Very important</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>survey_priorities_choices</t>
+          <t>data_privacy_priority_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_important'}</t>
+          <t>somewhat_important</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very_important'}</t>
+          <t>Somewhat important</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>survey_priorities_choices</t>
+          <t>data_privacy_priority_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_important'}</t>
+          <t>not_very_important</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat_important'}</t>
+          <t>Not very important</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>survey_priorities_choices</t>
+          <t>data_use_attitudes_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_important'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not_very_important'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>survey_concerns_choices</t>
+          <t>data_use_attitudes_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_concerned'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very_concerned'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>survey_concerns_choices</t>
+          <t>data_use_attitudes_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_concerned'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat_concerned'}</t>
+          <t>Neither satisfied nor dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>survey_concerns_choices</t>
+          <t>data_use_attitudes_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_very_concerned'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not_very_concerned'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>data_use_attitudes_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'male'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Male'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>likelihood_of_use_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'female'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Female'}</t>
+          <t>Very likely</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>likelihood_of_use_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Somewhat likely</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>likelihood_of_use_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Not likely</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>survey_satisfaction_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'hint':_'check_all_that_apply'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'hint': 'Check all that apply'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>survey_satisfaction_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>survey_satisfaction_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very_satisfied'}</t>
+          <t>Neither satisfied nor dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>survey_satisfaction_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Somewhat_satisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>survey_particip_choices</t>
+          <t>survey_satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neither_satisfied_nor_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Very_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very_likely'}</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very_likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat_likely'}</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat_likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'not_likely'}</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Not_likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very_satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat_satisfied'}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat_satisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'neither_satisfied_nor_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Neither_satisfied_nor_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'id':_4,_'label':_'somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'id': 4, 'label': 'Somewhat_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'id': 5, 'label': 'Very_dissatisfied'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_'very_likely'}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': 'Very_likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_'somewhat_likely'}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': 'Somewhat_likely'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>survey_particip_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'id':_3,_'label':_'not_likely'}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'id': 3, 'label': 'Not_likely'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
